--- a/Salary_Cap_2026.xlsx
+++ b/Salary_Cap_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Swish Swish\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Swish Swish\WNBA_SALARY_CAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB13E9A7-E15C-4813-A91A-7B57E451958C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4A4C2B-D47D-404F-992F-A48AA31CE8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="696" firstSheet="1" activeTab="15" xr2:uid="{05719DB4-8F06-45BC-9505-E988B961DE76}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="311">
   <si>
     <t>Player</t>
   </si>
@@ -729,9 +729,6 @@
     <t>Quionche Carter</t>
   </si>
   <si>
-    <t>Satou Sabally</t>
-  </si>
-  <si>
     <t>Monique Akoa Makani</t>
   </si>
   <si>
@@ -991,6 +988,21 @@
   </si>
   <si>
     <t>Megan McConnell</t>
+  </si>
+  <si>
+    <t>Yarden Garzon</t>
+  </si>
+  <si>
+    <t>Shay Ciezki</t>
+  </si>
+  <si>
+    <t>Kara Dunn</t>
+  </si>
+  <si>
+    <t>Jovana Nogic</t>
+  </si>
+  <si>
+    <t>Jihyun Park</t>
   </si>
 </sst>
 </file>
@@ -1976,14 +1988,14 @@
         <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>27</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Lynx!H2</f>
-        <v>1303590</v>
+        <v>836677</v>
       </c>
       <c r="I1" s="6"/>
     </row>
@@ -2010,7 +2022,7 @@
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
-        <v>5696410</v>
+        <v>6163323</v>
       </c>
       <c r="I2" s="6"/>
     </row>
@@ -2038,7 +2050,7 @@
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
-        <v>5148910</v>
+        <v>5615823</v>
       </c>
       <c r="I3" s="6"/>
     </row>
@@ -2068,7 +2080,7 @@
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4" s="6"/>
     </row>
@@ -2096,7 +2108,7 @@
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="6"/>
     </row>
@@ -2113,7 +2125,7 @@
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F6" s="11">
         <f>(C6/Cap!$B$1)*100</f>
@@ -2124,7 +2136,7 @@
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Lynx!H4)</f>
-        <v>325897.5</v>
+        <v>278892.33333333331</v>
       </c>
       <c r="I6" s="6"/>
     </row>
@@ -2148,11 +2160,11 @@
         <v>3.964285714285714</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
-        <v>81.377285714285719</v>
+        <v>88.047471428571427</v>
       </c>
       <c r="I7" s="6"/>
     </row>
@@ -2322,13 +2334,19 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="2"/>
+      <c r="B15" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C15" s="2">
+        <v>466913</v>
+      </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>300</v>
+      </c>
       <c r="F15" s="11">
         <f>(C15/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>6.6701857142857151</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -2552,10 +2570,10 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C29" s="7">
-        <v>466913</v>
+        <v>289133</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
@@ -2567,10 +2585,10 @@
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C30" s="7">
-        <v>289133</v>
+        <v>270000</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
@@ -2581,12 +2599,8 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
-      <c r="B31" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="C31" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="7"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -2690,7 +2704,7 @@
         <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>27</v>
@@ -2858,7 +2872,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
@@ -3390,14 +3404,14 @@
         <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>27</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Mercury!H2</f>
-        <v>2587500</v>
+        <v>2283900</v>
       </c>
       <c r="I1" s="6"/>
     </row>
@@ -3426,7 +3440,7 @@
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
-        <v>4412500</v>
+        <v>4716100</v>
       </c>
       <c r="I2" s="6"/>
     </row>
@@ -3484,7 +3498,7 @@
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I4" s="6"/>
     </row>
@@ -3494,7 +3508,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C5" s="2">
         <v>500000</v>
@@ -3542,7 +3556,7 @@
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Mercury!H4)</f>
-        <v>431250</v>
+        <v>456780</v>
       </c>
       <c r="I6" s="6"/>
     </row>
@@ -3566,11 +3580,11 @@
         <v>3.964285714285714</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
-        <v>63.035714285714285</v>
+        <v>67.372857142857143</v>
       </c>
       <c r="I7" s="6"/>
     </row>
@@ -3790,11 +3804,9 @@
         <v>219</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="2">
-        <v>2025</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="D17" s="2"/>
       <c r="E17" s="3"/>
       <c r="F17" s="11" t="e">
         <f>(C17/Cap!$B$1)*100</f>
@@ -3812,14 +3824,16 @@
       <c r="B18" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>17</v>
+      <c r="C18" s="2">
+        <v>303600</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="11" t="e">
+      <c r="E18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="11">
         <f>(C18/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>4.3371428571428572</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -3833,14 +3847,16 @@
       <c r="B19" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>17</v>
+      <c r="C19" s="2">
+        <v>277500</v>
       </c>
       <c r="D19" s="2"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="11" t="e">
+      <c r="E19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="11">
         <f>(C19/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -3855,7 +3871,7 @@
         <v>222</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="3"/>
@@ -3878,7 +3894,7 @@
       <c r="C21" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="11" t="e">
         <f>(C21/Cap!$B$1)*100</f>
@@ -3915,16 +3931,18 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="11" t="e">
+        <v>306</v>
+      </c>
+      <c r="C23" s="2">
+        <v>270000</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="11">
         <f>(C23/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
@@ -3935,13 +3953,19 @@
         <f>A23+1</f>
         <v>23</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
+      <c r="B24" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C24" s="2">
+        <v>270000</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="F24" s="11">
         <f>(C24/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
@@ -3952,13 +3976,19 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
+      <c r="B25" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C25" s="2">
+        <v>270000</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="F25" s="11">
         <f>(C25/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -3969,13 +3999,19 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
+      <c r="B26" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C26" s="2">
+        <v>270000</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="F26" s="11">
         <f>(C26/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
@@ -4012,7 +4048,7 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C29" s="7">
         <v>270000</v>
@@ -4027,7 +4063,7 @@
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C30" s="7">
         <v>270000</v>
@@ -4146,14 +4182,14 @@
         <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>27</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Fire!H2</f>
-        <v>3164091</v>
+        <v>2739091</v>
       </c>
       <c r="I1" s="6"/>
     </row>
@@ -4162,7 +4198,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C2" s="2">
         <v>1190000</v>
@@ -4182,7 +4218,7 @@
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
-        <v>3835909</v>
+        <v>4260909</v>
       </c>
       <c r="I2" s="6"/>
     </row>
@@ -4192,7 +4228,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C3" s="2">
         <v>500000</v>
@@ -4220,7 +4256,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C4" s="2">
         <v>360000</v>
@@ -4238,7 +4274,7 @@
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I4" s="6"/>
     </row>
@@ -4248,7 +4284,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C5" s="2">
         <v>325000</v>
@@ -4276,7 +4312,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C6" s="2">
         <v>300000</v>
@@ -4294,7 +4330,7 @@
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Fire!H4)</f>
-        <v>1054697</v>
+        <v>1369545.5</v>
       </c>
       <c r="I6" s="6"/>
     </row>
@@ -4304,7 +4340,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C7" s="2">
         <v>293510</v>
@@ -4318,11 +4354,11 @@
         <v>4.1930000000000005</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
-        <v>54.798699999999997</v>
+        <v>60.870128571428573</v>
       </c>
       <c r="I7" s="6"/>
     </row>
@@ -4332,7 +4368,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C8" s="2">
         <v>289133</v>
@@ -4355,7 +4391,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C9" s="2">
         <v>289133</v>
@@ -4378,7 +4414,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C10" s="2">
         <v>289133</v>
@@ -4401,7 +4437,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C11" s="2">
         <v>277500</v>
@@ -4424,7 +4460,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C12" s="2">
         <v>277500</v>
@@ -4447,7 +4483,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C13" s="2">
         <v>277500</v>
@@ -4470,16 +4506,18 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>96</v>
+        <v>239</v>
+      </c>
+      <c r="C14" s="2">
+        <v>425000</v>
       </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="11" t="e">
+      <c r="E14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="11">
         <f>(C14/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>6.0714285714285712</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -4695,7 +4733,7 @@
         <v>21</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -4720,7 +4758,7 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C29" s="7">
         <v>331563</v>
@@ -4735,7 +4773,7 @@
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C30" s="7">
         <v>270000</v>
@@ -4750,7 +4788,7 @@
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C31" s="7">
         <v>270000</v>
@@ -4819,6 +4857,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="F14" evalError="1"/>
+    <ignoredError sqref="H2:H3" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4858,7 +4897,7 @@
         <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>27</v>
@@ -4874,7 +4913,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C2" s="2">
         <v>1250000</v>
@@ -4904,7 +4943,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C3" s="2">
         <v>750000</v>
@@ -4932,7 +4971,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C4" s="2">
         <v>750000</v>
@@ -4960,7 +4999,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C5" s="2">
         <v>500000</v>
@@ -4988,7 +5027,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C6" s="2">
         <v>466913</v>
@@ -5016,7 +5055,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C7" s="2">
         <v>420000</v>
@@ -5030,7 +5069,7 @@
         <v>6</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
@@ -5044,14 +5083,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C8" s="2">
         <v>332278</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F8" s="11">
         <f>(C8/Cap!$B$1)*100</f>
@@ -5067,7 +5106,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C9" s="2">
         <v>277500</v>
@@ -5090,7 +5129,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C10" s="2">
         <v>277500</v>
@@ -5113,7 +5152,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C11" s="2">
         <v>277500</v>
@@ -5136,7 +5175,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>10</v>
@@ -5395,7 +5434,7 @@
         <v>21</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -5420,7 +5459,7 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C29" s="7">
         <v>436016</v>
@@ -5435,7 +5474,7 @@
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C30" s="7">
         <v>309622</v>
@@ -5450,7 +5489,7 @@
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C31" s="7">
         <v>289133</v>
@@ -5465,7 +5504,7 @@
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
       <c r="B32" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C32" s="7">
         <v>270000</v>
@@ -5563,14 +5602,14 @@
         <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>27</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Tempo!H2</f>
-        <v>3070543</v>
+        <v>1167985</v>
       </c>
       <c r="I1" s="6"/>
     </row>
@@ -5579,7 +5618,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C2" s="2">
         <v>1200000</v>
@@ -5599,7 +5638,7 @@
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
-        <v>3929457</v>
+        <v>5832015</v>
       </c>
       <c r="I2" s="6"/>
     </row>
@@ -5609,7 +5648,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C3" s="2">
         <v>1190000</v>
@@ -5627,7 +5666,7 @@
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
-        <v>3251957</v>
+        <v>4529457</v>
       </c>
       <c r="I3" s="6"/>
     </row>
@@ -5637,14 +5676,14 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C4" s="2">
         <v>436957</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F4" s="11">
         <f>(C4/Cap!$B$1)*100</f>
@@ -5655,7 +5694,7 @@
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I4" s="6"/>
     </row>
@@ -5665,7 +5704,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C5" s="2">
         <v>425000</v>
@@ -5683,7 +5722,7 @@
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I5" s="6"/>
     </row>
@@ -5693,7 +5732,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C6" s="2">
         <v>400000</v>
@@ -5711,7 +5750,7 @@
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Tempo!H4)</f>
-        <v>511757.16666666669</v>
+        <v>583992.5</v>
       </c>
       <c r="I6" s="6"/>
     </row>
@@ -5721,7 +5760,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C7" s="2">
         <v>277500</v>
@@ -5735,11 +5774,11 @@
         <v>3.964285714285714</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
-        <v>56.135100000000001</v>
+        <v>83.31450000000001</v>
       </c>
       <c r="I7" s="6"/>
     </row>
@@ -5749,7 +5788,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C8" s="2">
         <v>277500</v>
@@ -5772,7 +5811,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C9" s="2">
         <v>277500</v>
@@ -5795,7 +5834,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C10" s="2">
         <v>277500</v>
@@ -5818,7 +5857,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C11" s="2">
         <v>277500</v>
@@ -5841,7 +5880,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C12" s="2">
         <v>270000</v>
@@ -5864,7 +5903,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C13" s="2">
         <v>270000</v>
@@ -5887,7 +5926,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C14" s="2">
         <v>270000</v>
@@ -5910,7 +5949,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C15" s="2">
         <v>270000</v>
@@ -5933,7 +5972,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>17</v>
@@ -5953,13 +5992,19 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="2"/>
+      <c r="B17" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C17" s="2">
+        <v>355058</v>
+      </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="3"/>
+      <c r="E17" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F17" s="11">
         <f>(C17/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>5.0722571428571426</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -5970,13 +6015,19 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="2">
+        <v>277500</v>
+      </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="3"/>
+      <c r="E18" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="F18" s="11">
         <f>(C18/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -5987,13 +6038,19 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="2"/>
+      <c r="B19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1000000</v>
+      </c>
       <c r="D19" s="2"/>
-      <c r="E19" s="3"/>
+      <c r="E19" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="F19" s="11">
         <f>(C19/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -6004,13 +6061,19 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="2"/>
+      <c r="B20" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C20" s="2">
+        <v>270000</v>
+      </c>
       <c r="D20" s="2"/>
-      <c r="E20" s="3"/>
+      <c r="E20" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F20" s="11">
         <f>(C20/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -6124,7 +6187,7 @@
         <v>21</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -6152,7 +6215,7 @@
         <v>277</v>
       </c>
       <c r="C29" s="7">
-        <v>355058</v>
+        <v>270000</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
@@ -6193,12 +6256,8 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
-      <c r="B32" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="C32" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="7"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
@@ -6208,12 +6267,8 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
-      <c r="B33" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="C33" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B33" s="6"/>
+      <c r="C33" s="7"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
@@ -6295,14 +6350,14 @@
         <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>27</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Mystics!H2</f>
-        <v>3634263</v>
+        <v>3227100</v>
       </c>
       <c r="I1" s="6"/>
     </row>
@@ -6311,7 +6366,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C2" s="2">
         <v>1190000</v>
@@ -6329,7 +6384,7 @@
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
-        <v>3365737</v>
+        <v>3772900</v>
       </c>
       <c r="I2" s="6"/>
     </row>
@@ -6339,7 +6394,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C3" s="2">
         <v>700000</v>
@@ -6357,7 +6412,7 @@
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
-        <v>1890000</v>
+        <v>2297163</v>
       </c>
       <c r="I3" s="6"/>
     </row>
@@ -6367,7 +6422,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C4" s="2">
         <v>436016</v>
@@ -6385,7 +6440,7 @@
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I4" s="6"/>
     </row>
@@ -6395,7 +6450,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C5" s="2">
         <v>407163</v>
@@ -6413,7 +6468,7 @@
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" s="6"/>
     </row>
@@ -6423,7 +6478,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C6" s="2">
         <v>355058</v>
@@ -6441,7 +6496,7 @@
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Mystics!H4)</f>
-        <v>605710.5</v>
+        <v>645420</v>
       </c>
       <c r="I6" s="6"/>
     </row>
@@ -6451,7 +6506,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C7" s="2">
         <v>277500</v>
@@ -6465,11 +6520,11 @@
         <v>3.964285714285714</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
-        <v>48.081957142857142</v>
+        <v>53.898571428571429</v>
       </c>
       <c r="I7" s="6"/>
     </row>
@@ -6479,7 +6534,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C8" s="2">
         <v>277500</v>
@@ -6502,7 +6557,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C9" s="2">
         <v>270000</v>
@@ -6525,7 +6580,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>10</v>
@@ -6546,7 +6601,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>17</v>
@@ -6566,13 +6621,19 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2"/>
+      <c r="B12" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C12" s="2">
+        <v>407163</v>
+      </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>300</v>
+      </c>
       <c r="F12" s="11">
         <f>(C12/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>5.8166142857142855</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
@@ -6845,10 +6906,10 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C29" s="7">
-        <v>407163</v>
+        <v>289133</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
@@ -6860,7 +6921,7 @@
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C30" s="7">
         <v>289133</v>
@@ -6878,7 +6939,7 @@
         <v>294</v>
       </c>
       <c r="C31" s="7">
-        <v>289133</v>
+        <v>270000</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
@@ -6919,7 +6980,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="8" t="s">
         <v>297</v>
       </c>
       <c r="C34" s="7">
@@ -6948,12 +7009,8 @@
     </row>
     <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6"/>
-      <c r="B36" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="C36" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B36" s="8"/>
+      <c r="C36" s="7"/>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
@@ -7013,7 +7070,7 @@
         <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>27</v>
@@ -7189,7 +7246,7 @@
         <v>5.0098857142857138</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
@@ -7272,7 +7329,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C11" s="2">
         <v>277500</v>
@@ -7739,14 +7796,14 @@
         <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>27</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Sky!H2</f>
-        <v>524387</v>
+        <v>144168</v>
       </c>
       <c r="I1" s="6"/>
     </row>
@@ -7773,7 +7830,7 @@
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
-        <v>6475613</v>
+        <v>6855832</v>
       </c>
       <c r="I2" s="6"/>
     </row>
@@ -7801,7 +7858,7 @@
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
-        <v>4345000</v>
+        <v>4725219</v>
       </c>
       <c r="I3" s="6"/>
     </row>
@@ -7831,7 +7888,7 @@
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I4" s="6"/>
     </row>
@@ -7859,7 +7916,7 @@
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="6"/>
     </row>
@@ -7885,9 +7942,9 @@
       <c r="G6" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="H6" s="10" t="e">
+      <c r="H6" s="10">
         <f>H1/(Cap!B3-Sky!H4)</f>
-        <v>#DIV/0!</v>
+        <v>-144168</v>
       </c>
       <c r="I6" s="6"/>
     </row>
@@ -7911,11 +7968,11 @@
         <v>6.5881571428571428</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
-        <v>92.508757142857149</v>
+        <v>97.940457142857142</v>
       </c>
       <c r="I7" s="6"/>
     </row>
@@ -8086,10 +8143,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -8107,16 +8164,18 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>17</v>
+        <v>75</v>
+      </c>
+      <c r="C16" s="2">
+        <v>380219</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="11" t="e">
+      <c r="E16" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F16" s="11">
         <f>(C16/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>5.4316999999999993</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -8323,10 +8382,10 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C29" s="7">
-        <v>380219</v>
+        <v>289133</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
@@ -8338,10 +8397,10 @@
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C30" s="7">
-        <v>289133</v>
+        <v>270000</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
@@ -8353,7 +8412,7 @@
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C31" s="7">
         <v>270000</v>
@@ -8367,12 +8426,8 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
-      <c r="B32" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="7"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
@@ -8465,7 +8520,7 @@
         <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>27</v>
@@ -8574,7 +8629,7 @@
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F5" s="11">
         <f>(C5/Cap!$B$1)*100</f>
@@ -8637,7 +8692,7 @@
         <v>4.7366142857142854</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
@@ -8720,7 +8775,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C11" s="2">
         <v>277500</v>
@@ -9183,14 +9238,14 @@
         <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>27</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Wings!H2</f>
-        <v>839787</v>
+        <v>339787</v>
       </c>
       <c r="I1" s="6"/>
     </row>
@@ -9217,7 +9272,7 @@
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
-        <v>6160213</v>
+        <v>6660213</v>
       </c>
       <c r="I2" s="6"/>
     </row>
@@ -9247,7 +9302,7 @@
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
-        <v>4406080</v>
+        <v>4906080</v>
       </c>
       <c r="I3" s="6"/>
     </row>
@@ -9275,7 +9330,7 @@
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" s="6"/>
     </row>
@@ -9303,7 +9358,7 @@
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="6"/>
     </row>
@@ -9320,7 +9375,7 @@
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F6" s="11">
         <f>(C6/Cap!$B$1)*100</f>
@@ -9331,7 +9386,7 @@
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Wings!H4)</f>
-        <v>419893.5</v>
+        <v>339787</v>
       </c>
       <c r="I6" s="6"/>
     </row>
@@ -9355,11 +9410,11 @@
         <v>7.1428571428571423</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
-        <v>88.003042857142859</v>
+        <v>95.145900000000012</v>
       </c>
       <c r="I7" s="6"/>
     </row>
@@ -9599,10 +9654,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="3"/>
@@ -9620,16 +9675,14 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>10</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="11" t="e">
+      <c r="F19" s="11">
         <f>(C19/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -9641,16 +9694,18 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>19</v>
+        <v>122</v>
+      </c>
+      <c r="C20" s="2">
+        <v>500000</v>
       </c>
       <c r="D20" s="2"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="11" t="e">
+      <c r="E20" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F20" s="11">
         <f>(C20/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>7.1428571428571423</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -9789,10 +9844,10 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C29" s="7">
-        <v>500000</v>
+        <v>270000</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
@@ -9803,12 +9858,8 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
-      <c r="B30" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C30" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="7"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -9923,14 +9974,14 @@
         <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>27</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Valkyries!H2</f>
-        <v>1986271</v>
+        <v>1036271</v>
       </c>
       <c r="I1" s="6"/>
     </row>
@@ -9959,7 +10010,7 @@
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
-        <v>5013729</v>
+        <v>5963729</v>
       </c>
       <c r="I2" s="6"/>
     </row>
@@ -10015,7 +10066,7 @@
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I4" s="6"/>
     </row>
@@ -10071,7 +10122,7 @@
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Valkyries!H4)</f>
-        <v>496567.75</v>
+        <v>518135.5</v>
       </c>
       <c r="I6" s="6"/>
     </row>
@@ -10095,11 +10146,11 @@
         <v>5.4316999999999993</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
-        <v>71.62469999999999</v>
+        <v>85.196128571428574</v>
       </c>
       <c r="I7" s="6"/>
     </row>
@@ -10331,14 +10382,16 @@
       <c r="B18" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>17</v>
+      <c r="C18" s="2">
+        <v>450000</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="11" t="e">
+      <c r="E18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="11">
         <f>(C18/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>6.4285714285714279</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -10350,16 +10403,18 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>17</v>
+        <v>301</v>
+      </c>
+      <c r="C19" s="2">
+        <v>500000</v>
       </c>
       <c r="D19" s="2"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="11" t="e">
+      <c r="E19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="11">
         <f>(C19/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>7.1428571428571423</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -10653,14 +10708,14 @@
         <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>27</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Fever!H2</f>
-        <v>4219042</v>
+        <v>1311542</v>
       </c>
       <c r="I1" s="6"/>
     </row>
@@ -10676,7 +10731,7 @@
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F2" s="11">
         <f>(C2/Cap!$B$1)*100</f>
@@ -10687,7 +10742,7 @@
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
-        <v>2780958</v>
+        <v>5688458</v>
       </c>
       <c r="I2" s="6"/>
     </row>
@@ -10715,7 +10770,7 @@
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
-        <v>1974612</v>
+        <v>4204612</v>
       </c>
       <c r="I3" s="6"/>
     </row>
@@ -10743,7 +10798,7 @@
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I4" s="6"/>
     </row>
@@ -10773,7 +10828,7 @@
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I5" s="6"/>
     </row>
@@ -10799,7 +10854,7 @@
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Fever!H4)</f>
-        <v>527380.25</v>
+        <v>437180.66666666669</v>
       </c>
       <c r="I6" s="6"/>
     </row>
@@ -10811,21 +10866,23 @@
       <c r="B7" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>10</v>
+      <c r="C7" s="2">
+        <v>665000</v>
       </c>
       <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="11" t="e">
+      <c r="E7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="11">
         <f>(C7/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>9.5</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
-        <v>39.727971428571429</v>
+        <v>81.263685714285714</v>
       </c>
       <c r="I7" s="6"/>
     </row>
@@ -10837,14 +10894,16 @@
       <c r="B8" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>10</v>
+      <c r="C8" s="2">
+        <v>277500</v>
       </c>
       <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="11" t="e">
+      <c r="E8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="11">
         <f>(C8/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
@@ -10879,14 +10938,16 @@
       <c r="B10" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>96</v>
+      <c r="C10" s="2">
+        <v>765000</v>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="11" t="e">
+      <c r="E10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="11">
         <f>(C10/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>10.928571428571429</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
@@ -10898,7 +10959,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C11" s="2">
         <v>270000</v>
@@ -10920,13 +10981,17 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2"/>
+      <c r="B12" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="11">
+      <c r="F12" s="11" t="e">
         <f>(C12/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
@@ -10937,13 +11002,19 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="2"/>
+      <c r="B13" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" s="2">
+        <v>400000</v>
+      </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F13" s="11">
         <f>(C13/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>5.7142857142857144</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -10954,13 +11025,19 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="2"/>
+      <c r="B14" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" s="2">
+        <v>800000</v>
+      </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="F14" s="11">
         <f>(C14/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>11.428571428571429</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -11339,7 +11416,7 @@
         <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>27</v>
@@ -11511,7 +11588,7 @@
         <v>5.4285714285714288</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
@@ -12031,7 +12108,7 @@
         <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>27</v>
@@ -12207,7 +12284,7 @@
         <v>7.055014285714285</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
@@ -12292,14 +12369,16 @@
       <c r="B11" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>17</v>
+      <c r="C11" s="2">
+        <v>277500</v>
       </c>
       <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="11" t="e">
+      <c r="E11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="11">
         <f>(C11/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
@@ -12331,13 +12410,19 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="2"/>
+      <c r="B13" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C13" s="2">
+        <v>270000</v>
+      </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="F13" s="11">
         <f>(C13/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>

--- a/Salary_Cap_2026.xlsx
+++ b/Salary_Cap_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Swish Swish\WNBA_SALARY_CAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4A4C2B-D47D-404F-992F-A48AA31CE8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35ECBDD-4A5F-4BA2-8BE1-DA0BC0188B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="696" firstSheet="1" activeTab="15" xr2:uid="{05719DB4-8F06-45BC-9505-E988B961DE76}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="696" firstSheet="1" activeTab="1" xr2:uid="{05719DB4-8F06-45BC-9505-E988B961DE76}"/>
   </bookViews>
   <sheets>
     <sheet name="Cap" sheetId="2" state="hidden" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="354">
   <si>
     <t>Player</t>
   </si>
@@ -96,9 +96,6 @@
     <t>Sabrina Ionescu</t>
   </si>
   <si>
-    <t>Cored</t>
-  </si>
-  <si>
     <t>Natasha Cloud</t>
   </si>
   <si>
@@ -699,9 +696,6 @@
     <t>2015, 2016, 2018, 2019</t>
   </si>
   <si>
-    <t>Kalani Brown</t>
-  </si>
-  <si>
     <t>Kyara Linskens</t>
   </si>
   <si>
@@ -966,9 +960,6 @@
     <t>Rori Harmon</t>
   </si>
   <si>
-    <t>Txell Alarcon</t>
-  </si>
-  <si>
     <t>Angela Dugalic</t>
   </si>
   <si>
@@ -1003,6 +994,144 @@
   </si>
   <si>
     <t>Jihyun Park</t>
+  </si>
+  <si>
+    <t>Stephanie Jones</t>
+  </si>
+  <si>
+    <t>Bella Fontleroy</t>
+  </si>
+  <si>
+    <t>Laila Phelia</t>
+  </si>
+  <si>
+    <t>Sacha Washington</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Sydney Cooks</t>
+  </si>
+  <si>
+    <t>Megan Nestor</t>
+  </si>
+  <si>
+    <t>Jordan Hobbs</t>
+  </si>
+  <si>
+    <t>Harmoni Turner</t>
+  </si>
+  <si>
+    <t>Madison Hayes</t>
+  </si>
+  <si>
+    <t>Raegan Beers</t>
+  </si>
+  <si>
+    <t>Odyssey Sims</t>
+  </si>
+  <si>
+    <t>Grace Sullivan</t>
+  </si>
+  <si>
+    <t>Kyla Oldacre</t>
+  </si>
+  <si>
+    <t>Ndjakalenga Mwenentanda</t>
+  </si>
+  <si>
+    <t>Caroline Ducharme</t>
+  </si>
+  <si>
+    <t>Bailey Maupin</t>
+  </si>
+  <si>
+    <t>Kayana Traylor</t>
+  </si>
+  <si>
+    <t>Chennedy Carter</t>
+  </si>
+  <si>
+    <t>Liatu King</t>
+  </si>
+  <si>
+    <t>Jade Masogayo</t>
+  </si>
+  <si>
+    <t>Ra Shaya Kyle</t>
+  </si>
+  <si>
+    <t>Sakima Walker</t>
+  </si>
+  <si>
+    <t>Saylor Poffenbarger</t>
+  </si>
+  <si>
+    <t>Satou Sabally</t>
+  </si>
+  <si>
+    <t>DiDi Richards</t>
+  </si>
+  <si>
+    <t>Alex Fowler</t>
+  </si>
+  <si>
+    <t>Ashley Owusu</t>
+  </si>
+  <si>
+    <t>Derin Erdogan</t>
+  </si>
+  <si>
+    <t>Ny'Ceara Pryor</t>
+  </si>
+  <si>
+    <t>Ugonne Onyiah</t>
+  </si>
+  <si>
+    <t>Kalani Brown*</t>
+  </si>
+  <si>
+    <t>Jordan Harrison</t>
+  </si>
+  <si>
+    <t>Peyton Williams</t>
+  </si>
+  <si>
+    <t>Teja Oblak</t>
+  </si>
+  <si>
+    <t>Kamiah Smalls</t>
+  </si>
+  <si>
+    <t>Jaelyn Brown</t>
+  </si>
+  <si>
+    <t>Rennia Davis</t>
+  </si>
+  <si>
+    <t>Beatrice Mompremier</t>
+  </si>
+  <si>
+    <t>Elie Ladine</t>
+  </si>
+  <si>
+    <t>Jalyn Brown</t>
+  </si>
+  <si>
+    <t>Dara Mabrey</t>
+  </si>
+  <si>
+    <t>Christeen Iwuala</t>
+  </si>
+  <si>
+    <t>Kamaria McDaniel</t>
+  </si>
+  <si>
+    <t>Mya Hollingshed</t>
+  </si>
+  <si>
+    <t>Nyla Harris</t>
   </si>
 </sst>
 </file>
@@ -1507,7 +1636,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1536,6 +1665,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1926,7 +2058,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1">
         <v>7000000</v>
@@ -1934,7 +2066,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="1">
         <v>7</v>
@@ -1942,7 +2074,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1">
         <v>12</v>
@@ -1973,7 +2105,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -1985,13 +2117,13 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Lynx!H2</f>
@@ -2004,21 +2136,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C2" s="2">
         <v>1190000</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" s="11">
         <f>(C2/Cap!$B$1)*100</f>
         <v>17</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
@@ -2032,21 +2164,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C3" s="2">
         <v>1190000</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" s="11">
         <f>(C3/Cap!$B$1)*100</f>
         <v>17</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
@@ -2060,23 +2192,23 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C4" s="2">
         <v>700000</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" s="11">
         <f>(C4/Cap!$B$1)*100</f>
         <v>10</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
@@ -2090,21 +2222,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C5" s="2">
         <v>350000</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11">
         <f>(C5/Cap!$B$1)*100</f>
         <v>5</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
@@ -2118,21 +2250,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C6" s="2">
         <v>318910</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F6" s="11">
         <f>(C6/Cap!$B$1)*100</f>
         <v>4.5558571428571426</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Lynx!H4)</f>
@@ -2146,21 +2278,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C7" s="2">
         <v>277500</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" s="11">
         <f>(C7/Cap!$B$1)*100</f>
         <v>3.964285714285714</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
@@ -2174,14 +2306,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C8" s="2">
         <v>277500</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8" s="11">
         <f>(C8/Cap!$B$1)*100</f>
@@ -2197,14 +2329,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C9" s="2">
         <v>270000</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9" s="11">
         <f>(C9/Cap!$B$1)*100</f>
@@ -2220,14 +2352,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C10" s="2">
         <v>270000</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10" s="11">
         <f>(C10/Cap!$B$1)*100</f>
@@ -2243,14 +2375,14 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C11" s="2">
         <v>270000</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" s="11">
         <f>(C11/Cap!$B$1)*100</f>
@@ -2266,14 +2398,14 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C12" s="2">
         <v>270000</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" s="11">
         <f>(C12/Cap!$B$1)*100</f>
@@ -2289,14 +2421,14 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C13" s="2">
         <v>270000</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F13" s="11">
         <f>(C13/Cap!$B$1)*100</f>
@@ -2312,14 +2444,14 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C14" s="2">
         <v>1400000</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F14" s="11">
         <f>(C14/Cap!$B$1)*100</f>
@@ -2335,14 +2467,14 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C15" s="2">
         <v>466913</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F15" s="11">
         <f>(C15/Cap!$B$1)*100</f>
@@ -2357,13 +2489,19 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="2"/>
+      <c r="B16" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C16" s="2">
+        <v>277500</v>
+      </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="3"/>
+      <c r="E16" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F16" s="11">
         <f>(C16/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -2374,13 +2512,19 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="2"/>
+      <c r="B17" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C17" s="2">
+        <v>270000</v>
+      </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="3"/>
+      <c r="E17" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="F17" s="11">
         <f>(C17/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -2391,13 +2535,19 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C18" s="2">
+        <v>270000</v>
+      </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="3"/>
+      <c r="E18" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F18" s="11">
         <f>(C18/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -2408,13 +2558,19 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="2"/>
+      <c r="B19" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C19" s="2">
+        <v>270000</v>
+      </c>
       <c r="D19" s="2"/>
-      <c r="E19" s="3"/>
+      <c r="E19" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F19" s="11">
         <f>(C19/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -2425,13 +2581,19 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="2"/>
+      <c r="B20" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C20" s="2">
+        <v>270000</v>
+      </c>
       <c r="D20" s="2"/>
-      <c r="E20" s="3"/>
+      <c r="E20" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F20" s="11">
         <f>(C20/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -2442,13 +2604,19 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="2"/>
+      <c r="B21" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C21" s="2">
+        <v>270000</v>
+      </c>
       <c r="D21" s="2"/>
-      <c r="E21" s="3"/>
+      <c r="E21" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F21" s="11">
         <f>(C21/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -2459,13 +2627,19 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C22" s="2">
+        <v>270000</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F22" s="11">
         <f>(C22/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
@@ -2477,9 +2651,9 @@
         <v>22</v>
       </c>
       <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
       <c r="F23" s="11">
         <f>(C23/Cap!$B$1)*100</f>
         <v>0</v>
@@ -2494,9 +2668,9 @@
         <v>23</v>
       </c>
       <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
       <c r="F24" s="11">
         <f>(C24/Cap!$B$1)*100</f>
         <v>0</v>
@@ -2511,9 +2685,9 @@
         <v>24</v>
       </c>
       <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
       <c r="F25" s="11">
         <f>(C25/Cap!$B$1)*100</f>
         <v>0</v>
@@ -2528,9 +2702,9 @@
         <v>25</v>
       </c>
       <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
       <c r="F26" s="11">
         <f>(C26/Cap!$B$1)*100</f>
         <v>0</v>
@@ -2542,10 +2716,10 @@
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -2557,7 +2731,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="6"/>
@@ -2570,7 +2744,7 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C29" s="7">
         <v>289133</v>
@@ -2584,12 +2758,8 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
-      <c r="B30" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="C30" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="7"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -2689,7 +2859,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -2701,17 +2871,17 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Liberty!H2</f>
-        <v>6356490</v>
+        <v>1571490</v>
       </c>
       <c r="I1" s="6"/>
     </row>
@@ -2727,18 +2897,18 @@
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F2" s="11">
         <f>(C2/Cap!$B$1)*100</f>
         <v>5</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C1:C24, E1:E24, {"U";"V";"Rookie Scale"}))</f>
-        <v>643510</v>
+        <v>5428510</v>
       </c>
       <c r="I2" s="6"/>
     </row>
@@ -2755,18 +2925,18 @@
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3" s="11">
         <f>(C3/Cap!$B$1)*100</f>
         <v>4.1930000000000005</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C1:C24, E1:E24, {"V";"Rookie Scale"}))</f>
-        <v>0</v>
+        <v>4785000</v>
       </c>
       <c r="I3" s="6"/>
     </row>
@@ -2783,18 +2953,18 @@
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F4" s="11">
         <f>(C4/Cap!$B$1)*100</f>
         <v>3.8571428571428568</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I4" s="6"/>
     </row>
@@ -2811,18 +2981,18 @@
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11">
         <f>(C5/Cap!$B$1)*100</f>
         <v>3.8571428571428568</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I5" s="6"/>
     </row>
@@ -2839,18 +3009,18 @@
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F6" s="11">
         <f>(C6/Cap!$B$1)*100</f>
         <v>3.8571428571428568</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Liberty!H4)</f>
-        <v>635649</v>
+        <v>314298</v>
       </c>
       <c r="I6" s="6"/>
     </row>
@@ -2862,21 +3032,25 @@
       <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="11" t="e">
+      <c r="C7" s="2">
+        <v>1190000</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="11">
         <f>(C7/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>17</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
-        <v>9.1929999999999996</v>
+        <v>77.550142857142859</v>
       </c>
       <c r="I7" s="6"/>
     </row>
@@ -2886,16 +3060,20 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="11" t="e">
+      <c r="C8" s="2">
+        <v>1190000</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="11">
         <f>(C8/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>17</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
@@ -2907,18 +3085,20 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1190000</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="11" t="e">
+        <v>14</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="11">
         <f>(C9/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>17</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
@@ -2930,16 +3110,18 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
+      </c>
+      <c r="C10" s="2">
+        <v>400000</v>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="11" t="e">
+      <c r="E10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="11">
         <f>(C10/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>5.7142857142857144</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
@@ -2951,18 +3133,20 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="11" t="e">
+        <v>332</v>
+      </c>
+      <c r="C11" s="2">
+        <v>815000</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="11">
         <f>(C11/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>11.642857142857142</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
@@ -2974,16 +3158,18 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="C12" s="2">
+        <v>277500</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="11" t="e">
+      <c r="E12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="11">
         <f>(C12/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
@@ -2995,16 +3181,18 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="C13" s="2">
+        <v>277500</v>
       </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="11" t="e">
+      <c r="E13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="11">
         <f>(C13/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -3016,16 +3204,18 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>19</v>
+        <v>333</v>
+      </c>
+      <c r="C14" s="2">
+        <v>277500</v>
       </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="11" t="e">
+      <c r="E14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="11">
         <f>(C14/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -3037,16 +3227,18 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>19</v>
+        <v>334</v>
+      </c>
+      <c r="C15" s="2">
+        <v>270000</v>
       </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="11" t="e">
+      <c r="E15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="11">
         <f>(C15/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -3057,13 +3249,19 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="2"/>
+      <c r="B16" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C16" s="2">
+        <v>270000</v>
+      </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="3"/>
+      <c r="E16" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F16" s="11">
         <f>(C16/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -3074,13 +3272,19 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="2"/>
+      <c r="B17" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C17" s="2">
+        <v>270000</v>
+      </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="3"/>
+      <c r="E17" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F17" s="11">
         <f>(C17/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -3091,13 +3295,19 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C18" s="2">
+        <v>270000</v>
+      </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="3"/>
+      <c r="E18" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F18" s="11">
         <f>(C18/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -3108,13 +3318,19 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="2"/>
+      <c r="B19" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C19" s="2">
+        <v>270000</v>
+      </c>
       <c r="D19" s="2"/>
-      <c r="E19" s="3"/>
+      <c r="E19" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F19" s="11">
         <f>(C19/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -3125,13 +3341,17 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="2"/>
+      <c r="B20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="D20" s="2"/>
       <c r="E20" s="3"/>
-      <c r="F20" s="11">
+      <c r="F20" s="11" t="e">
         <f>(C20/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -3142,13 +3362,17 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="2"/>
+      <c r="B21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="D21" s="2"/>
       <c r="E21" s="3"/>
-      <c r="F21" s="11">
+      <c r="F21" s="11" t="e">
         <f>(C21/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -3159,13 +3383,17 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="11">
+      <c r="F22" s="11" t="e">
         <f>(C22/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
@@ -3177,7 +3405,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
+      <c r="C23" s="2"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="11">
@@ -3194,7 +3422,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
+      <c r="C24" s="2"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="11">
@@ -3211,7 +3439,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
+      <c r="C25" s="2"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="11">
@@ -3228,7 +3456,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
+      <c r="C26" s="2"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="11">
@@ -3242,10 +3470,10 @@
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -3257,7 +3485,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="6"/>
@@ -3270,7 +3498,7 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" s="7">
         <v>270000</v>
@@ -3285,7 +3513,7 @@
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C30" s="7">
         <v>270000</v>
@@ -3389,7 +3617,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -3401,17 +3629,17 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Mercury!H2</f>
-        <v>2283900</v>
+        <v>2161400</v>
       </c>
       <c r="I1" s="6"/>
     </row>
@@ -3420,27 +3648,27 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C2" s="2">
         <v>1200000</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" s="11">
         <f>(C2/Cap!$B$1)*100</f>
         <v>17.142857142857142</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
-        <v>4716100</v>
+        <v>4838600</v>
       </c>
       <c r="I2" s="6"/>
     </row>
@@ -3450,7 +3678,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C3" s="2">
         <v>1200000</v>
@@ -3459,18 +3687,18 @@
         <v>2025</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" s="11">
         <f>(C3/Cap!$B$1)*100</f>
         <v>17.142857142857142</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
-        <v>3912500</v>
+        <v>3735000</v>
       </c>
       <c r="I3" s="6"/>
     </row>
@@ -3480,25 +3708,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C4" s="2">
         <v>735000</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" s="11">
         <f>(C4/Cap!$B$1)*100</f>
         <v>10.5</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" s="6"/>
     </row>
@@ -3508,21 +3736,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C5" s="2">
         <v>500000</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11">
         <f>(C5/Cap!$B$1)*100</f>
         <v>7.1428571428571423</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
@@ -3536,27 +3764,27 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C6" s="2">
         <v>500000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" s="11">
         <f>(C6/Cap!$B$1)*100</f>
         <v>7.1428571428571423</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Mercury!H4)</f>
-        <v>456780</v>
+        <v>540350</v>
       </c>
       <c r="I6" s="6"/>
     </row>
@@ -3566,25 +3794,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>209</v>
+        <v>339</v>
       </c>
       <c r="C7" s="2">
-        <v>277500</v>
+        <v>100000</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F7" s="11">
         <f>(C7/Cap!$B$1)*100</f>
-        <v>3.964285714285714</v>
+        <v>1.4285714285714286</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
-        <v>67.372857142857143</v>
+        <v>69.122857142857143</v>
       </c>
       <c r="I7" s="6"/>
     </row>
@@ -3594,14 +3822,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C8" s="2">
         <v>277500</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8" s="11">
         <f>(C8/Cap!$B$1)*100</f>
@@ -3617,14 +3845,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C9" s="2">
         <v>277500</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9" s="11">
         <f>(C9/Cap!$B$1)*100</f>
@@ -3640,14 +3868,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C10" s="2">
         <v>277500</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10" s="11">
         <f>(C10/Cap!$B$1)*100</f>
@@ -3663,14 +3891,14 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C11" s="2">
         <v>277500</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" s="11">
         <f>(C11/Cap!$B$1)*100</f>
@@ -3686,14 +3914,14 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C12" s="2">
         <v>270000</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" s="11">
         <f>(C12/Cap!$B$1)*100</f>
@@ -3709,14 +3937,14 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C13" s="2">
         <v>270000</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F13" s="11">
         <f>(C13/Cap!$B$1)*100</f>
@@ -3732,14 +3960,14 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C14" s="2">
         <v>270000</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F14" s="11">
         <f>(C14/Cap!$B$1)*100</f>
@@ -3755,14 +3983,14 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C15" s="2">
         <v>270000</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F15" s="11">
         <f>(C15/Cap!$B$1)*100</f>
@@ -3778,14 +4006,14 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C16" s="2">
         <v>270000</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F16" s="11">
         <f>(C16/Cap!$B$1)*100</f>
@@ -3801,16 +4029,18 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>17</v>
+        <v>217</v>
+      </c>
+      <c r="C17" s="2">
+        <v>300000</v>
       </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="11" t="e">
+      <c r="E17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="11">
         <f>(C17/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>4.2857142857142856</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -3822,14 +4052,14 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2">
         <v>303600</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F18" s="11">
         <f>(C18/Cap!$B$1)*100</f>
@@ -3845,14 +4075,14 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2">
         <v>277500</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F19" s="11">
         <f>(C19/Cap!$B$1)*100</f>
@@ -3868,16 +4098,18 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>19</v>
+        <v>303</v>
+      </c>
+      <c r="C20" s="2">
+        <v>270000</v>
       </c>
       <c r="D20" s="2"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="11" t="e">
+      <c r="E20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="11">
         <f>(C20/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -3889,16 +4121,18 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>19</v>
+        <v>304</v>
+      </c>
+      <c r="C21" s="2">
+        <v>270000</v>
       </c>
       <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="11" t="e">
+      <c r="E21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="11">
         <f>(C21/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -3910,16 +4144,18 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>19</v>
+        <v>305</v>
+      </c>
+      <c r="C22" s="2">
+        <v>270000</v>
       </c>
       <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="11" t="e">
+      <c r="E22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="11">
         <f>(C22/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
@@ -3938,7 +4174,7 @@
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F23" s="11">
         <f>(C23/Cap!$B$1)*100</f>
@@ -3954,18 +4190,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C24" s="2">
-        <v>270000</v>
+        <v>220</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="D24" s="2"/>
-      <c r="E24" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F24" s="11">
+      <c r="E24" s="2"/>
+      <c r="F24" s="11" t="e">
         <f>(C24/Cap!$B$1)*100</f>
-        <v>3.8571428571428568</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
@@ -3977,18 +4211,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C25" s="2">
-        <v>270000</v>
+        <v>221</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="D25" s="2"/>
-      <c r="E25" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F25" s="11">
+      <c r="E25" s="2"/>
+      <c r="F25" s="11" t="e">
         <f>(C25/Cap!$B$1)*100</f>
-        <v>3.8571428571428568</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -4000,18 +4232,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C26" s="2">
-        <v>270000</v>
+        <v>222</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="D26" s="2"/>
-      <c r="E26" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26" s="11">
+      <c r="E26" s="2"/>
+      <c r="F26" s="11" t="e">
         <f>(C26/Cap!$B$1)*100</f>
-        <v>3.8571428571428568</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
@@ -4020,10 +4250,10 @@
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -4035,7 +4265,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="6"/>
@@ -4048,7 +4278,7 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C29" s="7">
         <v>270000</v>
@@ -4063,7 +4293,7 @@
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C30" s="7">
         <v>270000</v>
@@ -4167,7 +4397,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -4179,13 +4409,13 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Fire!H2</f>
@@ -4198,23 +4428,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C2" s="2">
         <v>1190000</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" s="11">
         <f>(C2/Cap!$B$1)*100</f>
         <v>17</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
@@ -4228,21 +4458,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C3" s="2">
         <v>500000</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" s="11">
         <f>(C3/Cap!$B$1)*100</f>
         <v>7.1428571428571423</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
@@ -4256,21 +4486,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C4" s="2">
         <v>360000</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" s="11">
         <f>(C4/Cap!$B$1)*100</f>
         <v>5.1428571428571423</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
@@ -4284,21 +4514,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C5" s="2">
         <v>325000</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5" s="11">
         <f>(C5/Cap!$B$1)*100</f>
         <v>4.6428571428571432</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
@@ -4312,21 +4542,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C6" s="2">
         <v>300000</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F6" s="11">
         <f>(C6/Cap!$B$1)*100</f>
         <v>4.2857142857142856</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Fire!H4)</f>
@@ -4340,21 +4570,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C7" s="2">
         <v>293510</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" s="11">
         <f>(C7/Cap!$B$1)*100</f>
         <v>4.1930000000000005</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
@@ -4368,14 +4598,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C8" s="2">
         <v>289133</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8" s="11">
         <f>(C8/Cap!$B$1)*100</f>
@@ -4391,14 +4621,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C9" s="2">
         <v>289133</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9" s="11">
         <f>(C9/Cap!$B$1)*100</f>
@@ -4414,14 +4644,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C10" s="2">
         <v>289133</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F10" s="11">
         <f>(C10/Cap!$B$1)*100</f>
@@ -4437,14 +4667,14 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C11" s="2">
         <v>277500</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" s="11">
         <f>(C11/Cap!$B$1)*100</f>
@@ -4460,14 +4690,14 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C12" s="2">
         <v>277500</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" s="11">
         <f>(C12/Cap!$B$1)*100</f>
@@ -4483,14 +4713,14 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C13" s="2">
         <v>277500</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F13" s="11">
         <f>(C13/Cap!$B$1)*100</f>
@@ -4506,14 +4736,14 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C14" s="2">
         <v>425000</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F14" s="11">
         <f>(C14/Cap!$B$1)*100</f>
@@ -4528,13 +4758,19 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="2"/>
+      <c r="B15" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="2">
+        <v>270000</v>
+      </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="F15" s="11">
         <f>(C15/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -4545,13 +4781,19 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="2"/>
+      <c r="B16" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C16" s="2">
+        <v>270000</v>
+      </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="3"/>
+      <c r="E16" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F16" s="11">
         <f>(C16/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -4562,13 +4804,19 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="2"/>
+      <c r="B17" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C17" s="2">
+        <v>270000</v>
+      </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="3"/>
+      <c r="E17" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F17" s="11">
         <f>(C17/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -4579,13 +4827,19 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C18" s="2">
+        <v>270000</v>
+      </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="3"/>
+      <c r="E18" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F18" s="11">
         <f>(C18/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -4596,13 +4850,19 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="2"/>
+      <c r="B19" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C19" s="2">
+        <v>270000</v>
+      </c>
       <c r="D19" s="2"/>
-      <c r="E19" s="3"/>
+      <c r="E19" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F19" s="11">
         <f>(C19/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -4730,10 +4990,10 @@
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -4745,7 +5005,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="6"/>
@@ -4758,7 +5018,7 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C29" s="7">
         <v>331563</v>
@@ -4773,7 +5033,7 @@
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C30" s="7">
         <v>270000</v>
@@ -4787,12 +5047,8 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
-      <c r="B31" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="C31" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="7"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -4882,7 +5138,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -4894,17 +5150,17 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Storm!H2</f>
-        <v>2253309</v>
+        <v>1817293</v>
       </c>
       <c r="I1" s="6"/>
     </row>
@@ -4913,27 +5169,27 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C2" s="2">
         <v>1250000</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" s="11">
         <f>(C2/Cap!$B$1)*100</f>
         <v>17.857142857142858</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
-        <v>4746691</v>
+        <v>5182707</v>
       </c>
       <c r="I2" s="6"/>
     </row>
@@ -4943,25 +5199,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C3" s="2">
         <v>750000</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" s="11">
         <f>(C3/Cap!$B$1)*100</f>
         <v>10.714285714285714</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
-        <v>4279778</v>
+        <v>4715794</v>
       </c>
       <c r="I3" s="6"/>
     </row>
@@ -4971,25 +5227,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C4" s="2">
         <v>750000</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" s="11">
         <f>(C4/Cap!$B$1)*100</f>
         <v>10.714285714285714</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4" s="6"/>
     </row>
@@ -4999,25 +5255,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C5" s="2">
         <v>500000</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11">
         <f>(C5/Cap!$B$1)*100</f>
         <v>7.1428571428571423</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" s="6"/>
     </row>
@@ -5027,25 +5283,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C6" s="2">
         <v>466913</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" s="11">
         <f>(C6/Cap!$B$1)*100</f>
         <v>6.6701857142857151</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Storm!H4)</f>
-        <v>563327.25</v>
+        <v>605764.33333333337</v>
       </c>
       <c r="I6" s="6"/>
     </row>
@@ -5055,25 +5311,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C7" s="2">
         <v>420000</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F7" s="11">
         <f>(C7/Cap!$B$1)*100</f>
         <v>6</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
-        <v>67.809871428571427</v>
+        <v>74.038671428571419</v>
       </c>
       <c r="I7" s="6"/>
     </row>
@@ -5083,14 +5339,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C8" s="2">
         <v>332278</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F8" s="11">
         <f>(C8/Cap!$B$1)*100</f>
@@ -5106,14 +5362,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C9" s="2">
         <v>277500</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" s="11">
         <f>(C9/Cap!$B$1)*100</f>
@@ -5129,14 +5385,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C10" s="2">
         <v>277500</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10" s="11">
         <f>(C10/Cap!$B$1)*100</f>
@@ -5152,14 +5408,14 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C11" s="2">
         <v>277500</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" s="11">
         <f>(C11/Cap!$B$1)*100</f>
@@ -5175,16 +5431,18 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>254</v>
+      </c>
+      <c r="C12" s="2">
+        <v>436016</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="11" t="e">
+      <c r="E12" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F12" s="11">
         <f>(C12/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>6.2288000000000006</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
@@ -5195,13 +5453,19 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="2"/>
+      <c r="B13" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C13" s="2">
+        <v>309622</v>
+      </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="F13" s="11">
         <f>(C13/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>4.4231714285714281</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -5212,13 +5476,19 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="2"/>
+      <c r="B14" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C14" s="2">
+        <v>289133</v>
+      </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="F14" s="11">
         <f>(C14/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>4.1304714285714281</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -5229,13 +5499,19 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="2"/>
+      <c r="B15" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C15" s="2">
+        <v>270000</v>
+      </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="F15" s="11">
         <f>(C15/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -5246,13 +5522,19 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="2"/>
+      <c r="B16" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C16" s="2">
+        <v>277500</v>
+      </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="3"/>
+      <c r="E16" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F16" s="11">
         <f>(C16/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -5263,13 +5545,19 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="2"/>
+      <c r="B17" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C17" s="2">
+        <v>277500</v>
+      </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="3"/>
+      <c r="E17" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F17" s="11">
         <f>(C17/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -5280,13 +5568,19 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C18" s="2">
+        <v>277500</v>
+      </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="3"/>
+      <c r="E18" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F18" s="11">
         <f>(C18/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -5297,13 +5591,19 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="2"/>
+      <c r="B19" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C19" s="2">
+        <v>270000</v>
+      </c>
       <c r="D19" s="2"/>
-      <c r="E19" s="3"/>
+      <c r="E19" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F19" s="11">
         <f>(C19/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -5314,13 +5614,19 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="2"/>
+      <c r="B20" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C20" s="2">
+        <v>270000</v>
+      </c>
       <c r="D20" s="2"/>
-      <c r="E20" s="3"/>
+      <c r="E20" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F20" s="11">
         <f>(C20/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -5416,13 +5722,17 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
+      <c r="B26" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
-      <c r="F26" s="11">
+      <c r="F26" s="11" t="e">
         <f>(C26/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
@@ -5431,10 +5741,10 @@
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -5446,7 +5756,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="6"/>
@@ -5458,12 +5768,8 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
-      <c r="B29" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="C29" s="7">
-        <v>436016</v>
-      </c>
+      <c r="B29" s="6"/>
+      <c r="C29" s="7"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
@@ -5473,12 +5779,8 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
-      <c r="B30" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="C30" s="7">
-        <v>309622</v>
-      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="7"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -5488,12 +5790,8 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
-      <c r="B31" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="C31" s="7">
-        <v>289133</v>
-      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="7"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -5503,12 +5801,8 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
-      <c r="B32" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="C32" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="7"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
@@ -5587,7 +5881,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -5599,17 +5893,17 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Tempo!H2</f>
-        <v>1167985</v>
+        <v>1793043</v>
       </c>
       <c r="I1" s="6"/>
     </row>
@@ -5618,27 +5912,27 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C2" s="2">
         <v>1200000</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" s="11">
         <f>(C2/Cap!$B$1)*100</f>
         <v>17.142857142857142</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
-        <v>5832015</v>
+        <v>5206957</v>
       </c>
       <c r="I2" s="6"/>
     </row>
@@ -5648,21 +5942,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C3" s="2">
         <v>1190000</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" s="11">
         <f>(C3/Cap!$B$1)*100</f>
         <v>17</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
@@ -5676,25 +5970,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C4" s="2">
         <v>436957</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F4" s="11">
         <f>(C4/Cap!$B$1)*100</f>
         <v>6.2422428571428572</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I4" s="6"/>
     </row>
@@ -5704,21 +5998,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C5" s="2">
         <v>425000</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11">
         <f>(C5/Cap!$B$1)*100</f>
         <v>6.0714285714285712</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
@@ -5732,25 +6026,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C6" s="2">
         <v>400000</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" s="11">
         <f>(C6/Cap!$B$1)*100</f>
         <v>5.7142857142857144</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Tempo!H4)</f>
-        <v>583992.5</v>
+        <v>448260.75</v>
       </c>
       <c r="I6" s="6"/>
     </row>
@@ -5760,25 +6054,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C7" s="2">
         <v>277500</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" s="11">
         <f>(C7/Cap!$B$1)*100</f>
         <v>3.964285714285714</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
-        <v>83.31450000000001</v>
+        <v>74.385100000000008</v>
       </c>
       <c r="I7" s="6"/>
     </row>
@@ -5788,14 +6082,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C8" s="2">
         <v>277500</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8" s="11">
         <f>(C8/Cap!$B$1)*100</f>
@@ -5811,14 +6105,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C9" s="2">
         <v>277500</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9" s="11">
         <f>(C9/Cap!$B$1)*100</f>
@@ -5834,14 +6128,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C10" s="2">
         <v>277500</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10" s="11">
         <f>(C10/Cap!$B$1)*100</f>
@@ -5857,14 +6151,14 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C11" s="2">
         <v>277500</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" s="11">
         <f>(C11/Cap!$B$1)*100</f>
@@ -5880,14 +6174,14 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C12" s="2">
         <v>270000</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" s="11">
         <f>(C12/Cap!$B$1)*100</f>
@@ -5903,14 +6197,14 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C13" s="2">
         <v>270000</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F13" s="11">
         <f>(C13/Cap!$B$1)*100</f>
@@ -5926,14 +6220,14 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C14" s="2">
         <v>270000</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F14" s="11">
         <f>(C14/Cap!$B$1)*100</f>
@@ -5949,14 +6243,14 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C15" s="2">
         <v>270000</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F15" s="11">
         <f>(C15/Cap!$B$1)*100</f>
@@ -5972,16 +6266,18 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>17</v>
+        <v>274</v>
+      </c>
+      <c r="C16" s="2">
+        <v>355058</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="11" t="e">
+      <c r="E16" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F16" s="11">
         <f>(C16/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>5.0722571428571426</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -5993,18 +6289,18 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>276</v>
+        <v>72</v>
       </c>
       <c r="C17" s="2">
-        <v>355058</v>
+        <v>277500</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F17" s="11">
         <f>(C17/Cap!$B$1)*100</f>
-        <v>5.0722571428571426</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -6016,18 +6312,18 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2">
-        <v>277500</v>
+        <v>1000000</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F18" s="11">
         <f>(C18/Cap!$B$1)*100</f>
-        <v>3.964285714285714</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -6039,18 +6335,18 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>135</v>
+        <v>278</v>
       </c>
       <c r="C19" s="2">
-        <v>1000000</v>
+        <v>270000</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>34</v>
+        <v>312</v>
       </c>
       <c r="F19" s="11">
         <f>(C19/Cap!$B$1)*100</f>
-        <v>14.285714285714285</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -6062,7 +6358,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>280</v>
+        <v>349</v>
       </c>
       <c r="C20" s="2">
         <v>270000</v>
@@ -6084,13 +6380,17 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="2"/>
+      <c r="B21" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="D21" s="2"/>
       <c r="E21" s="3"/>
-      <c r="F21" s="11">
+      <c r="F21" s="11" t="e">
         <f>(C21/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -6184,10 +6484,10 @@
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -6199,7 +6499,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="6"/>
@@ -6212,7 +6512,7 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C29" s="7">
         <v>270000</v>
@@ -6227,7 +6527,7 @@
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C30" s="7">
         <v>270000</v>
@@ -6242,7 +6542,7 @@
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C31" s="7">
         <v>270000</v>
@@ -6335,7 +6635,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -6347,13 +6647,13 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Mystics!H2</f>
@@ -6366,21 +6666,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C2" s="2">
         <v>1190000</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" s="11">
         <f>(C2/Cap!$B$1)*100</f>
         <v>17</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
@@ -6394,21 +6694,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C3" s="2">
         <v>700000</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" s="11">
         <f>(C3/Cap!$B$1)*100</f>
         <v>10</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
@@ -6422,21 +6722,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C4" s="2">
         <v>436016</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4" s="11">
         <f>(C4/Cap!$B$1)*100</f>
         <v>6.2288000000000006</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
@@ -6450,21 +6750,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C5" s="2">
         <v>407163</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5" s="11">
         <f>(C5/Cap!$B$1)*100</f>
         <v>5.8166142857142855</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
@@ -6478,21 +6778,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C6" s="2">
         <v>355058</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" s="11">
         <f>(C6/Cap!$B$1)*100</f>
         <v>5.0722571428571426</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Mystics!H4)</f>
@@ -6506,21 +6806,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C7" s="2">
         <v>277500</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" s="11">
         <f>(C7/Cap!$B$1)*100</f>
         <v>3.964285714285714</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
@@ -6534,14 +6834,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C8" s="2">
         <v>277500</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8" s="11">
         <f>(C8/Cap!$B$1)*100</f>
@@ -6557,14 +6857,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C9" s="2">
         <v>270000</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9" s="11">
         <f>(C9/Cap!$B$1)*100</f>
@@ -6582,14 +6882,16 @@
       <c r="B10" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>10</v>
+      <c r="C10" s="2">
+        <v>407163</v>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="11" t="e">
+      <c r="E10" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F10" s="11">
         <f>(C10/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>5.8166142857142855</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
@@ -6601,16 +6903,18 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>17</v>
+        <v>295</v>
+      </c>
+      <c r="C11" s="2">
+        <v>270000</v>
       </c>
       <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="11" t="e">
+      <c r="E11" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F11" s="11">
         <f>(C11/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
@@ -6625,15 +6929,15 @@
         <v>292</v>
       </c>
       <c r="C12" s="2">
-        <v>407163</v>
+        <v>270000</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="F12" s="11">
         <f>(C12/Cap!$B$1)*100</f>
-        <v>5.8166142857142855</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
@@ -6644,13 +6948,19 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="2"/>
+      <c r="B13" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C13" s="2">
+        <v>289133</v>
+      </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="F13" s="11">
         <f>(C13/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>4.1304714285714281</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -6661,13 +6971,19 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="2"/>
+      <c r="B14" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C14" s="2">
+        <v>289133</v>
+      </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="F14" s="11">
         <f>(C14/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>4.1304714285714281</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -6678,13 +6994,19 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="2"/>
+      <c r="B15" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C15" s="2">
+        <v>270000</v>
+      </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F15" s="11">
         <f>(C15/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -6695,13 +7017,19 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="2"/>
+      <c r="B16" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C16" s="2">
+        <v>270000</v>
+      </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="3"/>
+      <c r="E16" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F16" s="11">
         <f>(C16/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -6712,13 +7040,19 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="2"/>
+      <c r="B17" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C17" s="2">
+        <v>270000</v>
+      </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="3"/>
+      <c r="E17" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F17" s="11">
         <f>(C17/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -6729,13 +7063,19 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C18" s="2">
+        <v>270000</v>
+      </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="3"/>
+      <c r="E18" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F18" s="11">
         <f>(C18/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -6746,13 +7086,17 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="2"/>
+      <c r="B19" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="D19" s="2"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="11">
+      <c r="F19" s="11" t="e">
         <f>(C19/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -6866,7 +7210,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
+      <c r="C26" s="2"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="11">
@@ -6880,7 +7224,7 @@
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="6"/>
@@ -6893,7 +7237,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="6"/>
@@ -6906,10 +7250,10 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C29" s="7">
-        <v>289133</v>
+        <v>270000</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
@@ -6921,10 +7265,10 @@
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C30" s="7">
-        <v>289133</v>
+        <v>270000</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
@@ -6950,12 +7294,8 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
-      <c r="B32" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="C32" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="7"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
@@ -6965,12 +7305,8 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
-      <c r="B33" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="C33" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B33" s="6"/>
+      <c r="C33" s="7"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
@@ -6980,12 +7316,8 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
-      <c r="B34" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="C34" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B34" s="8"/>
+      <c r="C34" s="7"/>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
@@ -6995,12 +7327,8 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
-      <c r="B35" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="C35" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B35" s="8"/>
+      <c r="C35" s="7"/>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
@@ -7055,7 +7383,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -7067,13 +7395,13 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Dream!H2</f>
@@ -7086,23 +7414,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" s="2">
         <v>1190000</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" s="11">
         <f>(C2/Cap!$B$1)*100</f>
         <v>17</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
@@ -7116,21 +7444,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="2">
         <v>1100000</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" s="11">
         <f>(C3/Cap!$B$1)*100</f>
         <v>15.714285714285714</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
@@ -7144,23 +7472,23 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" s="2">
         <v>1000000</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" s="11">
         <f>(C4/Cap!$B$1)*100</f>
         <v>14.285714285714285</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
@@ -7174,21 +7502,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" s="2">
         <v>840000</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11">
         <f>(C5/Cap!$B$1)*100</f>
         <v>12</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
@@ -7202,23 +7530,23 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" s="2">
         <v>650000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F6" s="11">
         <f>(C6/Cap!$B$1)*100</f>
         <v>9.2857142857142865</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Dream!H4)</f>
@@ -7232,21 +7560,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="2">
         <v>350692</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" s="11">
         <f>(C7/Cap!$B$1)*100</f>
         <v>5.0098857142857138</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
@@ -7260,14 +7588,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" s="2">
         <v>277500</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8" s="11">
         <f>(C8/Cap!$B$1)*100</f>
@@ -7283,14 +7611,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" s="2">
         <v>277500</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9" s="11">
         <f>(C9/Cap!$B$1)*100</f>
@@ -7306,14 +7634,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C10" s="2">
         <v>277500</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10" s="11">
         <f>(C10/Cap!$B$1)*100</f>
@@ -7329,14 +7657,14 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C11" s="2">
         <v>277500</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" s="11">
         <f>(C11/Cap!$B$1)*100</f>
@@ -7352,14 +7680,14 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="2">
         <v>270000</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12" s="11">
         <f>(C12/Cap!$B$1)*100</f>
@@ -7375,14 +7703,14 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13" s="2">
         <v>270000</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F13" s="11">
         <f>(C13/Cap!$B$1)*100</f>
@@ -7398,14 +7726,14 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14" s="2">
         <v>270000</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F14" s="11">
         <f>(C14/Cap!$B$1)*100</f>
@@ -7421,16 +7749,18 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
+      </c>
+      <c r="C15" s="2">
+        <v>289133</v>
       </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="11" t="e">
+      <c r="E15" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F15" s="11">
         <f>(C15/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>4.1304714285714281</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -7442,16 +7772,18 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>17</v>
+        <v>57</v>
+      </c>
+      <c r="C16" s="2">
+        <v>270000</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="11" t="e">
+      <c r="E16" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F16" s="11">
         <f>(C16/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -7462,13 +7794,19 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="2"/>
+      <c r="B17" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C17" s="2">
+        <v>277500</v>
+      </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="3"/>
+      <c r="E17" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F17" s="11">
         <f>(C17/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -7479,13 +7817,19 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C18" s="2">
+        <v>270000</v>
+      </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="3"/>
+      <c r="E18" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F18" s="11">
         <f>(C18/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -7496,13 +7840,19 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="2"/>
+      <c r="B19" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C19" s="2">
+        <v>270000</v>
+      </c>
       <c r="D19" s="2"/>
-      <c r="E19" s="3"/>
+      <c r="E19" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F19" s="11">
         <f>(C19/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -7513,13 +7863,19 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="2"/>
+      <c r="B20" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C20" s="2">
+        <v>270000</v>
+      </c>
       <c r="D20" s="2"/>
-      <c r="E20" s="3"/>
+      <c r="E20" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F20" s="11">
         <f>(C20/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -7530,13 +7886,19 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="11">
+      <c r="B21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="11" t="e">
         <f>(C21/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -7548,9 +7910,9 @@
         <v>21</v>
       </c>
       <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
+      <c r="C22" s="2"/>
       <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
+      <c r="E22" s="2"/>
       <c r="F22" s="11">
         <f>(C22/Cap!$B$1)*100</f>
         <v>0</v>
@@ -7565,9 +7927,9 @@
         <v>22</v>
       </c>
       <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
+      <c r="C23" s="2"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
+      <c r="E23" s="2"/>
       <c r="F23" s="11">
         <f>(C23/Cap!$B$1)*100</f>
         <v>0</v>
@@ -7584,7 +7946,7 @@
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
+      <c r="E24" s="2"/>
       <c r="F24" s="11">
         <f>(C24/Cap!$B$1)*100</f>
         <v>0</v>
@@ -7601,7 +7963,7 @@
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
+      <c r="E25" s="2"/>
       <c r="F25" s="11">
         <f>(C25/Cap!$B$1)*100</f>
         <v>0</v>
@@ -7618,7 +7980,7 @@
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
+      <c r="E26" s="2"/>
       <c r="F26" s="11">
         <f>(C26/Cap!$B$1)*100</f>
         <v>0</v>
@@ -7630,10 +7992,10 @@
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -7645,7 +8007,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="6"/>
@@ -7658,10 +8020,10 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C29" s="7">
-        <v>289133</v>
+        <v>270000</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
@@ -7672,12 +8034,8 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
-      <c r="B30" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="7"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -7687,12 +8045,8 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
-      <c r="B31" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="7"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -7781,7 +8135,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -7793,17 +8147,17 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Sky!H2</f>
-        <v>144168</v>
+        <v>414168</v>
       </c>
       <c r="I1" s="6"/>
     </row>
@@ -7812,25 +8166,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" s="2">
         <v>1000000</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" s="11">
         <f>(C2/Cap!$B$1)*100</f>
         <v>14.285714285714285</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
-        <v>6855832</v>
+        <v>6585832</v>
       </c>
       <c r="I2" s="6"/>
     </row>
@@ -7840,21 +8194,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C3" s="2">
         <v>920000</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" s="11">
         <f>(C3/Cap!$B$1)*100</f>
         <v>13.142857142857142</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
@@ -7868,7 +8222,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C4" s="2">
         <v>750000</v>
@@ -7877,18 +8231,18 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" s="11">
         <f>(C4/Cap!$B$1)*100</f>
         <v>10.714285714285714</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I4" s="6"/>
     </row>
@@ -7898,21 +8252,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2">
         <v>650000</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11">
         <f>(C5/Cap!$B$1)*100</f>
         <v>9.2857142857142865</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
@@ -7926,25 +8280,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6" s="2">
         <v>600000</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F6" s="11">
         <f>(C6/Cap!$B$1)*100</f>
         <v>8.5714285714285712</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" s="10">
+        <v>59</v>
+      </c>
+      <c r="H6" s="10" t="e">
         <f>H1/(Cap!B3-Sky!H4)</f>
-        <v>-144168</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="I6" s="6"/>
     </row>
@@ -7954,25 +8308,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" s="2">
         <v>461171</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" s="11">
         <f>(C7/Cap!$B$1)*100</f>
         <v>6.5881571428571428</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
-        <v>97.940457142857142</v>
+        <v>94.08331428571428</v>
       </c>
       <c r="I7" s="6"/>
     </row>
@@ -7982,14 +8336,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" s="2">
         <v>430654</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8" s="11">
         <f>(C8/Cap!$B$1)*100</f>
@@ -8005,14 +8359,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9" s="2">
         <v>425000</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" s="11">
         <f>(C9/Cap!$B$1)*100</f>
@@ -8028,14 +8382,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C10" s="2">
         <v>402155</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F10" s="11">
         <f>(C10/Cap!$B$1)*100</f>
@@ -8051,14 +8405,14 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C11" s="2">
         <v>289133</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" s="11">
         <f>(C11/Cap!$B$1)*100</f>
@@ -8074,14 +8428,14 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C12" s="2">
         <v>277500</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12" s="11">
         <f>(C12/Cap!$B$1)*100</f>
@@ -8097,14 +8451,14 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C13" s="2">
         <v>270000</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>30</v>
+        <v>312</v>
       </c>
       <c r="F13" s="11">
         <f>(C13/Cap!$B$1)*100</f>
@@ -8120,14 +8474,14 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C14" s="2">
         <v>270000</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F14" s="11">
         <f>(C14/Cap!$B$1)*100</f>
@@ -8145,14 +8499,16 @@
       <c r="B15" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>17</v>
+      <c r="C15" s="2">
+        <v>380219</v>
       </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="11" t="e">
+      <c r="E15" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F15" s="11">
         <f>(C15/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>5.4316999999999993</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -8166,16 +8522,16 @@
       <c r="B16" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="2">
-        <v>380219</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2" t="s">
-        <v>300</v>
+      <c r="C16" s="13">
+        <v>270000</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13" t="s">
+        <v>312</v>
       </c>
       <c r="F16" s="11">
         <f>(C16/Cap!$B$1)*100</f>
-        <v>5.4316999999999993</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -8186,13 +8542,19 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="13">
+        <v>270000</v>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13" t="s">
+        <v>312</v>
+      </c>
       <c r="F17" s="11">
         <f>(C17/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -8203,13 +8565,19 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C18" s="13">
+        <v>270000</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13" t="s">
+        <v>30</v>
+      </c>
       <c r="F18" s="11">
         <f>(C18/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -8220,13 +8588,19 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="3"/>
+      <c r="B19" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C19" s="13">
+        <v>270000</v>
+      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13" t="s">
+        <v>30</v>
+      </c>
       <c r="F19" s="11">
         <f>(C19/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -8237,13 +8611,19 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="3"/>
+      <c r="B20" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C20" s="13">
+        <v>270000</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13" t="s">
+        <v>30</v>
+      </c>
       <c r="F20" s="11">
         <f>(C20/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -8254,13 +8634,17 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="11">
+      <c r="B21" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="11" t="e">
         <f>(C21/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -8272,9 +8656,9 @@
         <v>21</v>
       </c>
       <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
       <c r="F22" s="11">
         <f>(C22/Cap!$B$1)*100</f>
         <v>0</v>
@@ -8289,9 +8673,9 @@
         <v>22</v>
       </c>
       <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
       <c r="F23" s="11">
         <f>(C23/Cap!$B$1)*100</f>
         <v>0</v>
@@ -8306,9 +8690,9 @@
         <v>23</v>
       </c>
       <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
       <c r="F24" s="11">
         <f>(C24/Cap!$B$1)*100</f>
         <v>0</v>
@@ -8323,9 +8707,9 @@
         <v>24</v>
       </c>
       <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
       <c r="F25" s="11">
         <f>(C25/Cap!$B$1)*100</f>
         <v>0</v>
@@ -8340,9 +8724,9 @@
         <v>25</v>
       </c>
       <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
       <c r="F26" s="11">
         <f>(C26/Cap!$B$1)*100</f>
         <v>0</v>
@@ -8354,10 +8738,10 @@
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -8369,7 +8753,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="6"/>
@@ -8382,7 +8766,7 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C29" s="7">
         <v>289133</v>
@@ -8396,12 +8780,8 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
-      <c r="B30" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="7"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -8411,12 +8791,8 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
-      <c r="B31" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="7"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -8505,7 +8881,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -8517,13 +8893,13 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Sun!H2</f>
@@ -8536,23 +8912,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2">
         <v>1190000</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" s="11">
         <f>(C2/Cap!$B$1)*100</f>
         <v>17</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
@@ -8566,21 +8942,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C3" s="2">
         <v>1000000</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" s="11">
         <f>(C3/Cap!$B$1)*100</f>
         <v>14.285714285714285</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
@@ -8594,21 +8970,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2">
         <v>735000</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" s="11">
         <f>(C4/Cap!$B$1)*100</f>
         <v>10.5</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
@@ -8622,21 +8998,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2">
         <v>536588</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F5" s="11">
         <f>(C5/Cap!$B$1)*100</f>
         <v>7.6655428571428565</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
@@ -8650,21 +9026,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" s="2">
         <v>375542</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" s="11">
         <f>(C6/Cap!$B$1)*100</f>
         <v>5.3648857142857143</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Sun!H4)</f>
@@ -8678,21 +9054,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C7" s="2">
         <v>331563</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" s="11">
         <f>(C7/Cap!$B$1)*100</f>
         <v>4.7366142857142854</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
@@ -8706,14 +9082,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C8" s="2">
         <v>309622</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8" s="11">
         <f>(C8/Cap!$B$1)*100</f>
@@ -8729,14 +9105,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C9" s="2">
         <v>289133</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9" s="11">
         <f>(C9/Cap!$B$1)*100</f>
@@ -8752,14 +9128,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" s="2">
         <v>277500</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10" s="11">
         <f>(C10/Cap!$B$1)*100</f>
@@ -8775,14 +9151,14 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C11" s="2">
         <v>277500</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" s="11">
         <f>(C11/Cap!$B$1)*100</f>
@@ -8798,18 +9174,18 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="11" t="e">
+        <v>96</v>
+      </c>
+      <c r="C12" s="2">
+        <v>289133</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F12" s="11">
         <f>(C12/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>4.1304714285714281</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
@@ -8821,16 +9197,18 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>97</v>
+      </c>
+      <c r="C13" s="2">
+        <v>289133</v>
       </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="11" t="e">
+      <c r="E13" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F13" s="11">
         <f>(C13/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>4.1304714285714281</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -8842,16 +9220,18 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>98</v>
+      </c>
+      <c r="C14" s="2">
+        <v>270000</v>
       </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="11" t="e">
+      <c r="E14" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F14" s="11">
         <f>(C14/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -8863,16 +9243,18 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>96</v>
+        <v>240</v>
+      </c>
+      <c r="C15" s="2">
+        <v>270000</v>
       </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="11" t="e">
+      <c r="E15" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F15" s="11">
         <f>(C15/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -8883,13 +9265,19 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="2"/>
+      <c r="B16" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C16" s="2">
+        <v>270000</v>
+      </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="3"/>
+      <c r="E16" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F16" s="11">
         <f>(C16/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -8900,13 +9288,19 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="2"/>
+      <c r="B17" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C17" s="2">
+        <v>270000</v>
+      </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="3"/>
+      <c r="E17" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F17" s="11">
         <f>(C17/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -8917,13 +9311,19 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C18" s="2">
+        <v>270000</v>
+      </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="3"/>
+      <c r="E18" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F18" s="11">
         <f>(C18/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -8934,13 +9334,19 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="B19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="E19" s="3"/>
-      <c r="F19" s="11">
+      <c r="F19" s="11" t="e">
         <f>(C19/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -8951,13 +9357,17 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="2"/>
+      <c r="B20" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="D20" s="2"/>
       <c r="E20" s="3"/>
-      <c r="F20" s="11">
+      <c r="F20" s="11" t="e">
         <f>(C20/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -8968,13 +9378,17 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="2"/>
+      <c r="B21" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="D21" s="2"/>
       <c r="E21" s="3"/>
-      <c r="F21" s="11">
+      <c r="F21" s="11" t="e">
         <f>(C21/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -8985,13 +9399,17 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="2"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="11">
+      <c r="F22" s="11" t="e">
         <f>(C22/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
@@ -9003,8 +9421,8 @@
         <v>22</v>
       </c>
       <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
       <c r="E23" s="3"/>
       <c r="F23" s="11">
         <f>(C23/Cap!$B$1)*100</f>
@@ -9020,8 +9438,8 @@
         <v>23</v>
       </c>
       <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
       <c r="E24" s="3"/>
       <c r="F24" s="11">
         <f>(C24/Cap!$B$1)*100</f>
@@ -9037,8 +9455,8 @@
         <v>24</v>
       </c>
       <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
       <c r="E25" s="3"/>
       <c r="F25" s="11">
         <f>(C25/Cap!$B$1)*100</f>
@@ -9054,8 +9472,8 @@
         <v>25</v>
       </c>
       <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
       <c r="E26" s="3"/>
       <c r="F26" s="11">
         <f>(C26/Cap!$B$1)*100</f>
@@ -9068,10 +9486,10 @@
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -9083,7 +9501,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="6"/>
@@ -9095,12 +9513,8 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
-      <c r="B29" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" s="7">
-        <v>289133</v>
-      </c>
+      <c r="B29" s="6"/>
+      <c r="C29" s="7"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
@@ -9110,12 +9524,8 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
-      <c r="B30" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C30" s="7">
-        <v>289133</v>
-      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="7"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -9125,12 +9535,8 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
-      <c r="B31" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="7"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -9140,12 +9546,8 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
-      <c r="B32" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="7"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
@@ -9223,7 +9625,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -9235,13 +9637,13 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Wings!H2</f>
@@ -9254,21 +9656,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C2" s="2">
         <v>1190000</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" s="11">
         <f>(C2/Cap!$B$1)*100</f>
         <v>17</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
@@ -9282,23 +9684,23 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C3" s="2">
         <v>1190000</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" s="11">
         <f>(C3/Cap!$B$1)*100</f>
         <v>17</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
@@ -9312,21 +9714,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C4" s="2">
         <v>1000000</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" s="11">
         <f>(C4/Cap!$B$1)*100</f>
         <v>14.285714285714285</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
@@ -9340,21 +9742,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2">
         <v>525000</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11">
         <f>(C5/Cap!$B$1)*100</f>
         <v>7.5</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
@@ -9368,21 +9770,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2">
         <v>501080</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F6" s="11">
         <f>(C6/Cap!$B$1)*100</f>
         <v>7.1582857142857144</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Wings!H4)</f>
@@ -9396,21 +9798,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2">
         <v>500000</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" s="11">
         <f>(C7/Cap!$B$1)*100</f>
         <v>7.1428571428571423</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
@@ -9424,14 +9826,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C8" s="2">
         <v>410000</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8" s="11">
         <f>(C8/Cap!$B$1)*100</f>
@@ -9447,14 +9849,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2">
         <v>289133</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9" s="11">
         <f>(C9/Cap!$B$1)*100</f>
@@ -9470,14 +9872,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C10" s="2">
         <v>277500</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F10" s="11">
         <f>(C10/Cap!$B$1)*100</f>
@@ -9493,14 +9895,14 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2">
         <v>277500</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" s="11">
         <f>(C11/Cap!$B$1)*100</f>
@@ -9516,14 +9918,14 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C12" s="2">
         <v>277500</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" s="11">
         <f>(C12/Cap!$B$1)*100</f>
@@ -9539,14 +9941,14 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C13" s="2">
         <v>277500</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F13" s="11">
         <f>(C13/Cap!$B$1)*100</f>
@@ -9562,14 +9964,14 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C14" s="2">
         <v>277500</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F14" s="11">
         <f>(C14/Cap!$B$1)*100</f>
@@ -9585,14 +9987,14 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C15" s="2">
         <v>270000</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F15" s="11">
         <f>(C15/Cap!$B$1)*100</f>
@@ -9608,14 +10010,14 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C16" s="2">
         <v>270000</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F16" s="11">
         <f>(C16/Cap!$B$1)*100</f>
@@ -9631,14 +10033,14 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C17" s="2">
         <v>270000</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F17" s="11">
         <f>(C17/Cap!$B$1)*100</f>
@@ -9654,16 +10056,18 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>19</v>
+        <v>121</v>
+      </c>
+      <c r="C18" s="2">
+        <v>500000</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="11" t="e">
+      <c r="E18" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F18" s="11">
         <f>(C18/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>7.1428571428571423</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -9675,14 +10079,18 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="C19" s="2">
+        <v>277500</v>
+      </c>
       <c r="D19" s="2"/>
-      <c r="E19" s="3"/>
+      <c r="E19" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F19" s="11">
         <f>(C19/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -9694,18 +10102,18 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>122</v>
+        <v>319</v>
       </c>
       <c r="C20" s="2">
-        <v>500000</v>
+        <v>277500</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="F20" s="11">
         <f>(C20/Cap!$B$1)*100</f>
-        <v>7.1428571428571423</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -9716,13 +10124,19 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="2"/>
+      <c r="B21" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" s="2">
+        <v>270000</v>
+      </c>
       <c r="D21" s="2"/>
-      <c r="E21" s="3"/>
+      <c r="E21" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="F21" s="11">
         <f>(C21/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -9733,13 +10147,19 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C22" s="2">
+        <v>270000</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F22" s="11">
         <f>(C22/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
@@ -9750,13 +10170,19 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
+      <c r="B23" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C23" s="2">
+        <v>270000</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F23" s="11">
         <f>(C23/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
@@ -9767,13 +10193,17 @@
         <f>A23+1</f>
         <v>23</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
+      <c r="B24" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="11">
+      <c r="E24" s="2"/>
+      <c r="F24" s="11" t="e">
         <f>(C24/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
@@ -9785,9 +10215,9 @@
         <v>24</v>
       </c>
       <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
       <c r="F25" s="11">
         <f>(C25/Cap!$B$1)*100</f>
         <v>0</v>
@@ -9802,7 +10232,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
+      <c r="C26" s="2"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="11">
@@ -9816,10 +10246,10 @@
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -9831,7 +10261,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="6"/>
@@ -9843,12 +10273,8 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
-      <c r="B29" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C29" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B29" s="6"/>
+      <c r="C29" s="7"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
@@ -9959,7 +10385,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -9971,17 +10397,17 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Valkyries!H2</f>
-        <v>1036271</v>
+        <v>816490</v>
       </c>
       <c r="I1" s="6"/>
     </row>
@@ -9990,7 +10416,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C2" s="2">
         <v>1190000</v>
@@ -9999,18 +10425,18 @@
         <v>2025</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" s="11">
         <f>(C2/Cap!$B$1)*100</f>
         <v>17</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
-        <v>5963729</v>
+        <v>6183510</v>
       </c>
       <c r="I2" s="6"/>
     </row>
@@ -10020,25 +10446,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" s="2">
         <v>925000</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" s="11">
         <f>(C3/Cap!$B$1)*100</f>
         <v>13.214285714285715</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
-        <v>3840000</v>
+        <v>4440000</v>
       </c>
       <c r="I3" s="6"/>
     </row>
@@ -10048,21 +10474,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C4" s="2">
         <v>750000</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" s="11">
         <f>(C4/Cap!$B$1)*100</f>
         <v>10.714285714285714</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
@@ -10076,25 +10502,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C5" s="2">
         <v>600000</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11">
         <f>(C5/Cap!$B$1)*100</f>
         <v>8.5714285714285712</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="6"/>
     </row>
@@ -10104,25 +10530,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C6" s="2">
         <v>500000</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" s="11">
         <f>(C6/Cap!$B$1)*100</f>
         <v>7.1428571428571423</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Valkyries!H4)</f>
-        <v>518135.5</v>
+        <v>408245</v>
       </c>
       <c r="I6" s="6"/>
     </row>
@@ -10132,25 +10558,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C7" s="2">
         <v>380219</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>312</v>
       </c>
       <c r="F7" s="11">
         <f>(C7/Cap!$B$1)*100</f>
         <v>5.4316999999999993</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
-        <v>85.196128571428574</v>
+        <v>88.335857142857151</v>
       </c>
       <c r="I7" s="6"/>
     </row>
@@ -10160,14 +10586,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2">
         <v>375000</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8" s="11">
         <f>(C8/Cap!$B$1)*100</f>
@@ -10183,14 +10609,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C9" s="2">
         <v>293510</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9" s="11">
         <f>(C9/Cap!$B$1)*100</f>
@@ -10206,14 +10632,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C10" s="2">
         <v>270000</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10" s="11">
         <f>(C10/Cap!$B$1)*100</f>
@@ -10229,14 +10655,14 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="2">
         <v>270000</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" s="11">
         <f>(C11/Cap!$B$1)*100</f>
@@ -10252,14 +10678,14 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2">
         <v>270000</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" s="11">
         <f>(C12/Cap!$B$1)*100</f>
@@ -10275,16 +10701,18 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>135</v>
+      </c>
+      <c r="C13" s="2">
+        <v>600000</v>
       </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="11" t="e">
+      <c r="E13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="11">
         <f>(C13/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>8.5714285714285712</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -10296,16 +10724,18 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>136</v>
+      </c>
+      <c r="C14" s="2">
+        <v>277500</v>
       </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="11" t="e">
+      <c r="E14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="11">
         <f>(C14/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -10317,16 +10747,18 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>137</v>
+      </c>
+      <c r="C15" s="2">
+        <v>277500</v>
       </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="11" t="e">
+      <c r="E15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="11">
         <f>(C15/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -10338,16 +10770,18 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>17</v>
+        <v>138</v>
+      </c>
+      <c r="C16" s="2">
+        <v>450000</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="11" t="e">
+      <c r="E16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="11">
         <f>(C16/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>6.4285714285714279</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -10359,16 +10793,18 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>17</v>
+        <v>298</v>
+      </c>
+      <c r="C17" s="2">
+        <v>500000</v>
       </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="11" t="e">
+      <c r="E17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="11">
         <f>(C17/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>7.1428571428571423</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -10380,18 +10816,18 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C18" s="2">
-        <v>450000</v>
+        <v>270000</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
-        <v>30</v>
+        <v>312</v>
       </c>
       <c r="F18" s="11">
         <f>(C18/Cap!$B$1)*100</f>
-        <v>6.4285714285714279</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -10403,18 +10839,18 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>301</v>
+        <v>142</v>
       </c>
       <c r="C19" s="2">
-        <v>500000</v>
+        <v>270000</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>30</v>
+        <v>312</v>
       </c>
       <c r="F19" s="11">
         <f>(C19/Cap!$B$1)*100</f>
-        <v>7.1428571428571423</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -10425,13 +10861,19 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="2"/>
+      <c r="B20" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C20" s="2">
+        <v>270000</v>
+      </c>
       <c r="D20" s="2"/>
-      <c r="E20" s="3"/>
+      <c r="E20" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F20" s="11">
         <f>(C20/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -10442,13 +10884,19 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="2"/>
+      <c r="B21" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C21" s="2">
+        <v>270000</v>
+      </c>
       <c r="D21" s="2"/>
-      <c r="E21" s="3"/>
+      <c r="E21" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F21" s="11">
         <f>(C21/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -10459,13 +10907,19 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C22" s="2">
+        <v>270000</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F22" s="11">
         <f>(C22/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
@@ -10542,10 +10996,10 @@
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -10557,7 +11011,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="6"/>
@@ -10584,12 +11038,8 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
-      <c r="B30" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C30" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="7"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -10599,12 +11049,8 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
-      <c r="B31" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C31" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="7"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -10669,6 +11115,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="F13:F19" evalError="1"/>
+    <ignoredError sqref="H2:H3" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -10693,7 +11140,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -10705,17 +11152,17 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Fever!H2</f>
-        <v>1311542</v>
+        <v>571154</v>
       </c>
       <c r="I1" s="6"/>
     </row>
@@ -10724,25 +11171,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C2" s="2">
-        <v>574612</v>
+        <v>1000000</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F2" s="11">
         <f>(C2/Cap!$B$1)*100</f>
-        <v>8.2087428571428571</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
-        <v>5688458</v>
+        <v>6428846</v>
       </c>
       <c r="I2" s="6"/>
     </row>
@@ -10752,25 +11199,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C3" s="2">
         <v>528846</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3" s="11">
         <f>(C3/Cap!$B$1)*100</f>
         <v>7.5549428571428576</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
-        <v>4204612</v>
+        <v>4945000</v>
       </c>
       <c r="I3" s="6"/>
     </row>
@@ -10780,25 +11227,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4" s="2">
         <v>277500</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4" s="11">
         <f>(C4/Cap!$B$1)*100</f>
         <v>3.964285714285714</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I4" s="6"/>
     </row>
@@ -10808,27 +11255,27 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C5" s="2">
         <v>1400000</v>
       </c>
-      <c r="D5" s="2">
-        <v>2025</v>
+      <c r="D5" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11">
         <f>(C5/Cap!$B$1)*100</f>
         <v>20</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="6"/>
     </row>
@@ -10838,23 +11285,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>133</v>
+      </c>
+      <c r="C6" s="2">
+        <v>800000</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="11" t="e">
+      <c r="E6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="11">
         <f>(C6/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>11.428571428571429</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Fever!H4)</f>
-        <v>437180.66666666669</v>
+        <v>285577</v>
       </c>
       <c r="I6" s="6"/>
     </row>
@@ -10864,25 +11313,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C7" s="2">
         <v>665000</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F7" s="11">
         <f>(C7/Cap!$B$1)*100</f>
         <v>9.5</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
-        <v>81.263685714285714</v>
+        <v>91.84065714285714</v>
       </c>
       <c r="I7" s="6"/>
     </row>
@@ -10892,14 +11341,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C8" s="2">
         <v>277500</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8" s="11">
         <f>(C8/Cap!$B$1)*100</f>
@@ -10915,16 +11364,18 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>118</v>
+      </c>
+      <c r="C9" s="2">
+        <v>315000</v>
       </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="11" t="e">
+      <c r="E9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="11">
         <f>(C9/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>4.5</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
@@ -10936,14 +11387,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C10" s="2">
         <v>765000</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F10" s="11">
         <f>(C10/Cap!$B$1)*100</f>
@@ -10959,14 +11410,14 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C11" s="2">
         <v>270000</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" s="11">
         <f>(C11/Cap!$B$1)*100</f>
@@ -10982,16 +11433,18 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>152</v>
+      </c>
+      <c r="C12" s="2">
+        <v>289133</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="11" t="e">
+      <c r="E12" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F12" s="11">
         <f>(C12/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>4.1304714285714281</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
@@ -11003,14 +11456,14 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2">
         <v>400000</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F13" s="11">
         <f>(C13/Cap!$B$1)*100</f>
@@ -11026,18 +11479,18 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="C14" s="2">
-        <v>800000</v>
+        <v>270000</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>34</v>
+        <v>312</v>
       </c>
       <c r="F14" s="11">
         <f>(C14/Cap!$B$1)*100</f>
-        <v>11.428571428571429</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -11048,13 +11501,19 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="2"/>
+      <c r="B15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="2">
+        <v>277500</v>
+      </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F15" s="11">
         <f>(C15/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -11065,13 +11524,19 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="2"/>
+      <c r="B16" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C16" s="2">
+        <v>270000</v>
+      </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="3"/>
+      <c r="E16" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F16" s="11">
         <f>(C16/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -11082,13 +11547,17 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="2"/>
+      <c r="B17" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="D17" s="2"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="11">
+      <c r="F17" s="11" t="e">
         <f>(C17/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -11099,13 +11568,17 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="D18" s="2"/>
       <c r="E18" s="3"/>
-      <c r="F18" s="11">
+      <c r="F18" s="11" t="e">
         <f>(C18/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -11219,7 +11692,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
+      <c r="C25" s="2"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="11">
@@ -11236,7 +11709,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
+      <c r="C26" s="2"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="11">
@@ -11250,10 +11723,10 @@
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -11265,7 +11738,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="6"/>
@@ -11278,10 +11751,10 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C29" s="7">
-        <v>289133</v>
+        <v>270000</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
@@ -11292,12 +11765,8 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
-      <c r="B30" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C30" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="7"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -11307,12 +11776,6 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
-      <c r="B31" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C31" s="7">
-        <v>270000</v>
-      </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -11401,7 +11864,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -11413,13 +11876,13 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Vegas!H2</f>
@@ -11432,21 +11895,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C2" s="2">
         <v>1190000</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" s="11">
         <f>(C2/Cap!$B$1)*100</f>
         <v>17</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
@@ -11460,21 +11923,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C3" s="2">
         <v>1000000</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" s="11">
         <f>(C3/Cap!$B$1)*100</f>
         <v>14.285714285714285</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
@@ -11488,23 +11951,23 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C4" s="2">
         <v>800000</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" s="11">
         <f>(C4/Cap!$B$1)*100</f>
         <v>11.428571428571429</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
@@ -11518,21 +11981,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C5" s="2">
         <v>450000</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11">
         <f>(C5/Cap!$B$1)*100</f>
         <v>6.4285714285714279</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
@@ -11546,21 +12009,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C6" s="2">
         <v>392500</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F6" s="11">
         <f>(C6/Cap!$B$1)*100</f>
         <v>5.6071428571428568</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Vegas!H4)</f>
@@ -11574,21 +12037,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C7" s="2">
         <v>380000</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F7" s="11">
         <f>(C7/Cap!$B$1)*100</f>
         <v>5.4285714285714288</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
@@ -11602,14 +12065,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C8" s="2">
         <v>277500</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8" s="11">
         <f>(C8/Cap!$B$1)*100</f>
@@ -11625,14 +12088,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C9" s="2">
         <v>277500</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9" s="11">
         <f>(C9/Cap!$B$1)*100</f>
@@ -11648,14 +12111,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C10" s="2">
         <v>277500</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10" s="11">
         <f>(C10/Cap!$B$1)*100</f>
@@ -11671,14 +12134,14 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" s="2">
         <v>1400000</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11" s="11">
         <f>(C11/Cap!$B$1)*100</f>
@@ -11693,13 +12156,19 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2"/>
+      <c r="B12" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C12" s="2">
+        <v>277500</v>
+      </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F12" s="11">
         <f>(C12/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
@@ -11710,13 +12179,19 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="2"/>
+      <c r="B13" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C13" s="2">
+        <v>270000</v>
+      </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="F13" s="11">
         <f>(C13/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -11727,13 +12202,19 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="2"/>
+      <c r="B14" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C14" s="2">
+        <v>270000</v>
+      </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="F14" s="11">
         <f>(C14/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -11946,10 +12427,10 @@
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -11961,7 +12442,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="6"/>
@@ -11973,12 +12454,8 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
-      <c r="B29" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C29" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B29" s="6"/>
+      <c r="C29" s="7"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
@@ -11988,12 +12465,8 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
-      <c r="B30" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C30" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="7"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -12093,7 +12566,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -12105,13 +12578,13 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1" s="7">
         <f>Cap!B1-Sparks!H2</f>
@@ -12124,21 +12597,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C2" s="2">
         <v>1100000</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" s="11">
         <f>(C2/Cap!$B$1)*100</f>
         <v>15.714285714285714</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H2" s="7" cm="1">
         <f t="array" ref="H2">SUM(SUMIFS(C2:C26, E2:E26, {"U";"V";"Rookie Scale"}))</f>
@@ -12152,23 +12625,23 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C3" s="2">
         <v>1085000</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" s="11">
         <f>(C3/Cap!$B$1)*100</f>
         <v>15.5</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3" s="7" cm="1">
         <f t="array" ref="H3">SUM(SUMIFS(C2:C26, E2:E26, {"V";"Rookie Scale"}))</f>
@@ -12182,23 +12655,23 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C4" s="2">
         <v>999999</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" s="11">
         <f>(C4/Cap!$B$1)*100</f>
         <v>14.285700000000002</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4" s="7" cm="1">
         <f t="array" ref="H4">SUM(COUNTIF(E2:E26,{"U";"V";"Rookie Scale"}))</f>
@@ -12212,23 +12685,23 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C5" s="2">
         <v>950000</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11">
         <f>(C5/Cap!$B$1)*100</f>
         <v>13.571428571428571</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="7" cm="1">
         <f t="array" ref="H5">SUM(COUNTIF(E2:E26,{"V";"Rookie Scale"}))</f>
@@ -12242,21 +12715,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C6" s="2">
         <v>625000</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F6" s="11">
         <f>(C6/Cap!$B$1)*100</f>
         <v>8.9285714285714288</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H6" s="10">
         <f>H1/(Cap!B3-Sparks!H4)</f>
@@ -12270,21 +12743,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C7" s="2">
         <v>493851</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" s="11">
         <f>(C7/Cap!$B$1)*100</f>
         <v>7.055014285714285</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H7" s="12">
         <f>(H2/Cap!$B$1)*100</f>
@@ -12298,14 +12771,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C8" s="2">
         <v>277500</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8" s="11">
         <f>(C8/Cap!$B$1)*100</f>
@@ -12321,14 +12794,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C9" s="2">
         <v>277500</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9" s="11">
         <f>(C9/Cap!$B$1)*100</f>
@@ -12344,14 +12817,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C10" s="2">
         <v>277500</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10" s="11">
         <f>(C10/Cap!$B$1)*100</f>
@@ -12367,14 +12840,14 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C11" s="2">
         <v>277500</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" s="11">
         <f>(C11/Cap!$B$1)*100</f>
@@ -12390,16 +12863,18 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>17</v>
+        <v>307</v>
+      </c>
+      <c r="C12" s="2">
+        <v>270000</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="11" t="e">
+      <c r="E12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="11">
         <f>(C12/Cap!$B$1)*100</f>
-        <v>#VALUE!</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
@@ -12411,14 +12886,14 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>310</v>
+        <v>181</v>
       </c>
       <c r="C13" s="2">
         <v>270000</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>31</v>
+        <v>312</v>
       </c>
       <c r="F13" s="11">
         <f>(C13/Cap!$B$1)*100</f>
@@ -12433,13 +12908,19 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="2"/>
+      <c r="B14" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C14" s="2">
+        <v>270000</v>
+      </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="F14" s="11">
         <f>(C14/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -12450,13 +12931,19 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="2"/>
+      <c r="B15" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C15" s="2">
+        <v>270000</v>
+      </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="F15" s="11">
         <f>(C15/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>3.8571428571428568</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -12467,13 +12954,17 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="2"/>
+      <c r="B16" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="D16" s="2"/>
       <c r="E16" s="3"/>
-      <c r="F16" s="11">
+      <c r="F16" s="11" t="e">
         <f>(C16/Cap!$B$1)*100</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -12638,7 +13129,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
+      <c r="C26" s="2"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="11">
@@ -12652,10 +13143,10 @@
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -12667,7 +13158,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="6"/>
@@ -12679,12 +13170,8 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
-      <c r="B29" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="C29" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B29" s="6"/>
+      <c r="C29" s="7"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
@@ -12694,12 +13181,8 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
-      <c r="B30" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C30" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="7"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -12709,12 +13192,8 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
-      <c r="B31" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C31" s="7">
-        <v>270000</v>
-      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="7"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
